--- a/Excels/#Ammo.xlsx
+++ b/Excels/#Ammo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -49,6 +49,54 @@
   </si>
   <si>
     <t>player_ammo_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>velocity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>质量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dampening</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反弹衰减</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>life</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -398,10 +446,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -411,8 +463,23 @@
       <c r="C1" t="s">
         <v>4</v>
       </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -422,18 +489,57 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/#Ammo.xlsx
+++ b/Excels/#Ammo.xlsx
@@ -449,8 +449,11 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6328125" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="4" max="5" width="14.6328125" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">

--- a/Excels/#Ammo.xlsx
+++ b/Excels/#Ammo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,56 +48,62 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>damage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>velocity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>质量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dampening</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>反弹衰减</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>life</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_ammo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enemy_ammo_1</t>
+  </si>
+  <si>
     <t>player_ammo_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>damage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>velocity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>速度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mass</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>质量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dampening</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>反弹衰减</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>life</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -446,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.54296875" customWidth="1"/>
@@ -467,19 +473,19 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -493,19 +499,19 @@
         <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -513,13 +519,13 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -527,7 +533,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D4">
         <v>100</v>
@@ -542,6 +548,29 @@
         <v>1</v>
       </c>
       <c r="H4">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>0.6</v>
       </c>
     </row>

--- a/Excels/#Ammo.xlsx
+++ b/Excels/#Ammo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -104,6 +104,14 @@
   </si>
   <si>
     <t>player_ammo_1</t>
+  </si>
+  <si>
+    <t>dead_events</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>array,string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -452,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.54296875" customWidth="1"/>
@@ -462,7 +470,7 @@
     <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,8 +495,11 @@
       <c r="H1" t="s">
         <v>15</v>
       </c>
+      <c r="I1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -513,8 +524,11 @@
       <c r="H2" t="s">
         <v>16</v>
       </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -528,7 +542,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -551,7 +565,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>20</v>
       </c>

--- a/Excels/#Ammo.xlsx
+++ b/Excels/#Ammo.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,12 +106,43 @@
     <t>player_ammo_1</t>
   </si>
   <si>
-    <t>dead_events</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>array,string</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plane_AimBullet01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plane_AimBullet02</t>
+  </si>
+  <si>
+    <t>Plane_AimBullet03</t>
+  </si>
+  <si>
+    <t>Plane_AimBullet04</t>
+  </si>
+  <si>
+    <t>dead_trigger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Plane_HomingMissiles01</t>
+  </si>
+  <si>
+    <t>Plane_HomingMissiles02</t>
+  </si>
+  <si>
+    <t>Fort_Laser01</t>
+  </si>
+  <si>
+    <t>Fort_Scatter01</t>
+  </si>
+  <si>
+    <t>Fort_Scatter02</t>
+  </si>
+  <si>
+    <t>Fort_Scatter03</t>
   </si>
 </sst>
 </file>
@@ -460,14 +491,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
-    <col min="3" max="3" width="19.81640625" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="29.453125" customWidth="1"/>
     <col min="4" max="5" width="14.6328125" customWidth="1"/>
-    <col min="6" max="6" width="15.54296875" customWidth="1"/>
-    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" customWidth="1"/>
+    <col min="7" max="7" width="10.81640625" customWidth="1"/>
+    <col min="8" max="8" width="15.26953125" customWidth="1"/>
+    <col min="9" max="9" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -496,7 +529,7 @@
         <v>15</v>
       </c>
       <c r="I1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -525,7 +558,7 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -585,6 +618,236 @@
         <v>1</v>
       </c>
       <c r="H5">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <v>100</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <v>100</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9">
+        <v>100</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <v>100</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>100</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13">
+        <v>100</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
+      <c r="E14">
+        <v>100</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>100</v>
+      </c>
+      <c r="E15">
+        <v>100</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
         <v>0.6</v>
       </c>
     </row>
